--- a/trades_log.xlsx
+++ b/trades_log.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="26">
   <si>
     <t>Timestamp</t>
   </si>
@@ -61,88 +61,37 @@
     <t>Exit Reason</t>
   </si>
   <si>
-    <t>2026-08-04 13:49:12</t>
+    <t>2026-08-04 16:34:37</t>
   </si>
   <si>
     <t>BTCUSDT</t>
   </si>
   <si>
+    <t>LONG</t>
+  </si>
+  <si>
+    <t>1x</t>
+  </si>
+  <si>
+    <t>CVD Reversal (&gt;20% Drop)</t>
+  </si>
+  <si>
+    <t>2026-08-04 16:45:54</t>
+  </si>
+  <si>
     <t>SHORT</t>
   </si>
   <si>
-    <t>5x</t>
-  </si>
-  <si>
-    <t>OBI (1.09) &gt; 0.70</t>
-  </si>
-  <si>
-    <t>2026-08-04 13:49:43</t>
-  </si>
-  <si>
-    <t>OBI (0.95) &gt; 0.70</t>
-  </si>
-  <si>
-    <t>2026-08-04 13:49:45</t>
-  </si>
-  <si>
-    <t>OBI (0.81) &gt; 0.70</t>
-  </si>
-  <si>
-    <t>2026-08-04 13:49:46</t>
-  </si>
-  <si>
-    <t>OBI (0.82) &gt; 0.70</t>
-  </si>
-  <si>
-    <t>2026-08-04 13:49:50</t>
-  </si>
-  <si>
-    <t>OBI (0.79) &gt; 0.70</t>
-  </si>
-  <si>
-    <t>2026-08-04 13:49:52</t>
-  </si>
-  <si>
-    <t>OBI (0.80) &gt; 0.70</t>
-  </si>
-  <si>
-    <t>2026-08-04 13:49:53</t>
-  </si>
-  <si>
-    <t>OBI (0.90) &gt; 0.70</t>
-  </si>
-  <si>
-    <t>2026-08-04 13:49:54</t>
-  </si>
-  <si>
-    <t>OBI (0.78) &gt; 0.70</t>
-  </si>
-  <si>
-    <t>2026-08-04 13:49:55</t>
-  </si>
-  <si>
-    <t>OBI (0.91) &gt; 0.70</t>
-  </si>
-  <si>
-    <t>2026-08-04 13:50:40</t>
-  </si>
-  <si>
-    <t>LONG</t>
-  </si>
-  <si>
-    <t>OBI (1.18) &lt; 1.20</t>
-  </si>
-  <si>
-    <t>2026-08-04 13:51:01</t>
-  </si>
-  <si>
-    <t>OBI (1.58) &gt; 0.70</t>
-  </si>
-  <si>
-    <t>2026-08-04 13:52:19</t>
-  </si>
-  <si>
-    <t>OBI (1.06) &gt; 0.70</t>
+    <t>Price Returned Inside Breakout Range</t>
+  </si>
+  <si>
+    <t>2026-08-04 16:52:37</t>
+  </si>
+  <si>
+    <t>Take Profit (+0.15%)</t>
+  </si>
+  <si>
+    <t>2026-08-04 16:53:01</t>
   </si>
 </sst>
 </file>
@@ -211,7 +160,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -224,6 +173,7 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -518,7 +468,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
@@ -531,11 +481,11 @@
     <col min="8" max="8" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="20" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="21" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="22" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="23" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="34.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
@@ -599,34 +549,34 @@
         <v>18</v>
       </c>
       <c r="E2" s="3">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F2" s="3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G2" s="4">
-        <v>0.0007862088897268128</v>
+        <v>0.0015690877167106273</v>
       </c>
       <c r="H2" s="3">
-        <v>63596.33</v>
+        <v>63731.3</v>
       </c>
       <c r="I2" s="3">
-        <v>63594.99</v>
+        <v>63748.8</v>
       </c>
       <c r="J2" s="2">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="K2" s="5">
-        <v>0.0010535199122369038</v>
+        <v>0.027459035042435978</v>
       </c>
       <c r="L2" s="3">
-        <v>0.09999894648008777</v>
+        <v>0.10001372951752123</v>
       </c>
       <c r="M2" s="6">
-        <v>-0.09894542656785087</v>
+        <v>-0.07255469447508525</v>
       </c>
       <c r="N2" s="7">
-        <v>-0.009894542656785087</v>
+        <v>-0.0007255469447508525</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>19</v>
@@ -640,48 +590,48 @@
         <v>16</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E3" s="3">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F3" s="3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G3" s="4">
-        <v>0.0007862254558102769</v>
+        <v>0.0015701199885695264</v>
       </c>
       <c r="H3" s="3">
-        <v>63594.99</v>
+        <v>63689.4</v>
       </c>
       <c r="I3" s="3">
-        <v>63594.98</v>
+        <v>63692.9</v>
       </c>
       <c r="J3" s="2">
-        <v>5</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0.000007862254553983978</v>
+        <v>0</v>
+      </c>
+      <c r="K3" s="6">
+        <v>-0.005495419959993342</v>
       </c>
       <c r="L3" s="3">
-        <v>0.09999999213774544</v>
+        <v>0.10000274770997998</v>
       </c>
       <c r="M3" s="6">
-        <v>-0.09999212988319145</v>
+        <v>-0.10549816766997332</v>
       </c>
       <c r="N3" s="7">
-        <v>-0.009999212988319146</v>
+        <v>-0.0010549816766997331</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>16</v>
@@ -693,42 +643,42 @@
         <v>18</v>
       </c>
       <c r="E4" s="3">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F4" s="3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G4" s="4">
-        <v>0.0007862255794403898</v>
+        <v>0.0015695482526219304</v>
       </c>
       <c r="H4" s="3">
-        <v>63594.98</v>
+        <v>63712.6</v>
       </c>
       <c r="I4" s="3">
-        <v>63594.99</v>
+        <v>63808.2</v>
       </c>
       <c r="J4" s="2">
-        <v>0</v>
-      </c>
-      <c r="K4" s="6">
-        <v>-0.000007862255790285105</v>
+        <v>182</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0.15004881295065425</v>
       </c>
       <c r="L4" s="3">
-        <v>0.10000000786225578</v>
-      </c>
-      <c r="M4" s="6">
-        <v>-0.10000787011804607</v>
-      </c>
-      <c r="N4" s="7">
-        <v>-0.010000787011804606</v>
+        <v>0.10007502440647534</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0.049973788544178915</v>
+      </c>
+      <c r="N4" s="8">
+        <v>0.0004997378854417891</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>16</v>
@@ -740,507 +690,37 @@
         <v>18</v>
       </c>
       <c r="E5" s="3">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F5" s="3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G5" s="4">
-        <v>0.0007862255794403898</v>
+        <v>0.0015671328364477487</v>
       </c>
       <c r="H5" s="3">
-        <v>63594.98</v>
+        <v>63810.8</v>
       </c>
       <c r="I5" s="3">
-        <v>63594.99</v>
+        <v>63810.4</v>
       </c>
       <c r="J5" s="2">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K5" s="6">
-        <v>-0.000007862255790285105</v>
+        <v>-0.0006268531345813799</v>
       </c>
       <c r="L5" s="3">
-        <v>0.10000000786225578</v>
+        <v>0.09999968657343271</v>
       </c>
       <c r="M5" s="6">
-        <v>-0.10000787011804607</v>
+        <v>-0.10062653970801409</v>
       </c>
       <c r="N5" s="7">
-        <v>-0.010000787011804606</v>
+        <v>-0.001006265397080141</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
-      <c r="A6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="3">
-        <v>10</v>
-      </c>
-      <c r="F6" s="3">
-        <v>50</v>
-      </c>
-      <c r="G6" s="4">
-        <v>0.0007862254558102769</v>
-      </c>
-      <c r="H6" s="3">
-        <v>63594.99</v>
-      </c>
-      <c r="I6" s="3">
-        <v>63594.99</v>
-      </c>
-      <c r="J6" s="2">
-        <v>2</v>
-      </c>
-      <c r="K6" s="5">
-        <v>0</v>
-      </c>
-      <c r="L6" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="M6" s="6">
-        <v>-0.1</v>
-      </c>
-      <c r="N6" s="7">
-        <v>-0.01</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
-      <c r="A7" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="3">
-        <v>10</v>
-      </c>
-      <c r="F7" s="3">
-        <v>50</v>
-      </c>
-      <c r="G7" s="4">
-        <v>0.0007862254558102769</v>
-      </c>
-      <c r="H7" s="3">
-        <v>63594.99</v>
-      </c>
-      <c r="I7" s="3">
-        <v>63594.98</v>
-      </c>
-      <c r="J7" s="2">
-        <v>2</v>
-      </c>
-      <c r="K7" s="5">
-        <v>0.000007862254553983978</v>
-      </c>
-      <c r="L7" s="3">
-        <v>0.09999999213774544</v>
-      </c>
-      <c r="M7" s="6">
-        <v>-0.09999212988319145</v>
-      </c>
-      <c r="N7" s="7">
-        <v>-0.009999212988319146</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
-      <c r="A8" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="3">
-        <v>10</v>
-      </c>
-      <c r="F8" s="3">
-        <v>50</v>
-      </c>
-      <c r="G8" s="4">
-        <v>0.0007862255794403898</v>
-      </c>
-      <c r="H8" s="3">
-        <v>63594.98</v>
-      </c>
-      <c r="I8" s="3">
-        <v>63594.98</v>
-      </c>
-      <c r="J8" s="2">
-        <v>0</v>
-      </c>
-      <c r="K8" s="5">
-        <v>0</v>
-      </c>
-      <c r="L8" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="M8" s="6">
-        <v>-0.1</v>
-      </c>
-      <c r="N8" s="7">
-        <v>-0.01</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
-      <c r="A9" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" s="3">
-        <v>10</v>
-      </c>
-      <c r="F9" s="3">
-        <v>50</v>
-      </c>
-      <c r="G9" s="4">
-        <v>0.0007862255794403898</v>
-      </c>
-      <c r="H9" s="3">
-        <v>63594.98</v>
-      </c>
-      <c r="I9" s="3">
-        <v>63594.99</v>
-      </c>
-      <c r="J9" s="2">
-        <v>0</v>
-      </c>
-      <c r="K9" s="6">
-        <v>-0.000007862255790285105</v>
-      </c>
-      <c r="L9" s="3">
-        <v>0.10000000786225578</v>
-      </c>
-      <c r="M9" s="6">
-        <v>-0.10000787011804607</v>
-      </c>
-      <c r="N9" s="7">
-        <v>-0.010000787011804606</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
-      <c r="A10" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" s="3">
-        <v>10</v>
-      </c>
-      <c r="F10" s="3">
-        <v>50</v>
-      </c>
-      <c r="G10" s="4">
-        <v>0.0007862255794403898</v>
-      </c>
-      <c r="H10" s="3">
-        <v>63594.98</v>
-      </c>
-      <c r="I10" s="3">
-        <v>63594.98</v>
-      </c>
-      <c r="J10" s="2">
-        <v>0</v>
-      </c>
-      <c r="K10" s="5">
-        <v>0</v>
-      </c>
-      <c r="L10" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="M10" s="6">
-        <v>-0.1</v>
-      </c>
-      <c r="N10" s="7">
-        <v>-0.01</v>
-      </c>
-      <c r="O10" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
-      <c r="A11" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E11" s="3">
-        <v>10</v>
-      </c>
-      <c r="F11" s="3">
-        <v>50</v>
-      </c>
-      <c r="G11" s="4">
-        <v>0.0007862255794403898</v>
-      </c>
-      <c r="H11" s="3">
-        <v>63594.98</v>
-      </c>
-      <c r="I11" s="3">
-        <v>63594.98</v>
-      </c>
-      <c r="J11" s="2">
-        <v>0</v>
-      </c>
-      <c r="K11" s="5">
-        <v>0</v>
-      </c>
-      <c r="L11" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="M11" s="6">
-        <v>-0.1</v>
-      </c>
-      <c r="N11" s="7">
-        <v>-0.01</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
-      <c r="A12" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E12" s="3">
-        <v>10</v>
-      </c>
-      <c r="F12" s="3">
-        <v>50</v>
-      </c>
-      <c r="G12" s="4">
-        <v>0.0007862255794403898</v>
-      </c>
-      <c r="H12" s="3">
-        <v>63594.98</v>
-      </c>
-      <c r="I12" s="3">
-        <v>63594.98</v>
-      </c>
-      <c r="J12" s="2">
-        <v>0</v>
-      </c>
-      <c r="K12" s="5">
-        <v>0</v>
-      </c>
-      <c r="L12" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="M12" s="6">
-        <v>-0.1</v>
-      </c>
-      <c r="N12" s="7">
-        <v>-0.01</v>
-      </c>
-      <c r="O12" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
-      <c r="A13" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E13" s="3">
-        <v>10</v>
-      </c>
-      <c r="F13" s="3">
-        <v>50</v>
-      </c>
-      <c r="G13" s="4">
-        <v>0.0007862254558102769</v>
-      </c>
-      <c r="H13" s="3">
-        <v>63594.99</v>
-      </c>
-      <c r="I13" s="3">
-        <v>63594.99</v>
-      </c>
-      <c r="J13" s="2">
-        <v>10</v>
-      </c>
-      <c r="K13" s="5">
-        <v>0</v>
-      </c>
-      <c r="L13" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="M13" s="6">
-        <v>-0.1</v>
-      </c>
-      <c r="N13" s="7">
-        <v>-0.01</v>
-      </c>
-      <c r="O13" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
-      <c r="A14" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E14" s="3">
-        <v>10</v>
-      </c>
-      <c r="F14" s="3">
-        <v>50</v>
-      </c>
-      <c r="G14" s="4">
-        <v>0.0007862255794403898</v>
-      </c>
-      <c r="H14" s="3">
-        <v>63594.98</v>
-      </c>
-      <c r="I14" s="3">
-        <v>63594.98</v>
-      </c>
-      <c r="J14" s="2">
-        <v>7</v>
-      </c>
-      <c r="K14" s="5">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="M14" s="6">
-        <v>-0.1</v>
-      </c>
-      <c r="N14" s="7">
-        <v>-0.01</v>
-      </c>
-      <c r="O14" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
-      <c r="A15" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E15" s="3">
-        <v>10</v>
-      </c>
-      <c r="F15" s="3">
-        <v>50</v>
-      </c>
-      <c r="G15" s="4">
-        <v>0.0007862255794403898</v>
-      </c>
-      <c r="H15" s="3">
-        <v>63594.98</v>
-      </c>
-      <c r="I15" s="3">
-        <v>63594.99</v>
-      </c>
-      <c r="J15" s="2">
-        <v>24</v>
-      </c>
-      <c r="K15" s="6">
-        <v>-0.000007862255790285105</v>
-      </c>
-      <c r="L15" s="3">
-        <v>0.10000000786225578</v>
-      </c>
-      <c r="M15" s="6">
-        <v>-0.10000787011804607</v>
-      </c>
-      <c r="N15" s="7">
-        <v>-0.010000787011804606</v>
-      </c>
-      <c r="O15" s="2" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
